--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirotaRyou\Documents\GitHub\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BE4108-B9F0-4782-A0CD-922588488F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54A5964-AF24-446B-BC09-00E5753A388A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="67">
   <si>
     <t>アルファ</t>
   </si>
@@ -376,6 +376,10 @@
     <rPh sb="6" eb="8">
       <t>ジカン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aaa</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -821,7 +825,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1003,12 +1007,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1519,7 +1517,9 @@
         <v>48</v>
       </c>
       <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="I6" t="s">
         <v>25</v>
       </c>
@@ -1911,7 +1911,7 @@
       <c r="G17" s="4"/>
       <c r="H17" s="5"/>
       <c r="L17" s="25"/>
-      <c r="M17" s="63">
+      <c r="M17" s="61">
         <v>27</v>
       </c>
       <c r="N17" s="43">
@@ -1920,7 +1920,7 @@
       <c r="O17" s="43">
         <v>29</v>
       </c>
-      <c r="P17" s="62">
+      <c r="P17" s="26">
         <v>30</v>
       </c>
       <c r="Q17" s="29">
@@ -2053,9 +2053,6 @@
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="5"/>
-      <c r="L25" s="61"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="61"/>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B26" s="4"/>
@@ -2069,9 +2066,6 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="5"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="61"/>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B27" s="4"/>
@@ -2085,9 +2079,6 @@
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="5"/>
-      <c r="L27" s="61"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="61"/>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B28" s="4"/>

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BE4108-B9F0-4782-A0CD-922588488F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B16310-F3ED-44EF-BBA1-01D3B50BCA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="67">
   <si>
     <t>アルファ</t>
   </si>
@@ -376,6 +376,10 @@
     <rPh sb="6" eb="8">
       <t>ジカン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -821,7 +825,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1003,12 +1007,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1638,6 +1636,9 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="5"/>
+      <c r="I9" t="s">
+        <v>66</v>
+      </c>
       <c r="L9" s="10"/>
       <c r="M9" s="18">
         <v>8</v>
@@ -1911,7 +1912,7 @@
       <c r="G17" s="4"/>
       <c r="H17" s="5"/>
       <c r="L17" s="25"/>
-      <c r="M17" s="63">
+      <c r="M17" s="61">
         <v>27</v>
       </c>
       <c r="N17" s="43">
@@ -1920,7 +1921,7 @@
       <c r="O17" s="43">
         <v>29</v>
       </c>
-      <c r="P17" s="62">
+      <c r="P17" s="26">
         <v>30</v>
       </c>
       <c r="Q17" s="29">
@@ -2053,9 +2054,6 @@
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="5"/>
-      <c r="L25" s="61"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="61"/>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B26" s="4"/>
@@ -2069,9 +2067,6 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="5"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="61"/>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B27" s="4"/>
@@ -2085,9 +2080,6 @@
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="5"/>
-      <c r="L27" s="61"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="61"/>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B28" s="4"/>

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirotaRyou\Documents\GitHub\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B16310-F3ED-44EF-BBA1-01D3B50BCA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1BB7D5-D16D-472F-A54A-9DBDCF57C303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
   <si>
     <t>アルファ</t>
   </si>
@@ -380,6 +380,10 @@
   </si>
   <si>
     <t>a</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aaa</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1674,6 +1678,9 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="5"/>
+      <c r="I10" t="s">
+        <v>67</v>
+      </c>
       <c r="L10" s="10"/>
       <c r="M10" s="18">
         <v>15</v>

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B16310-F3ED-44EF-BBA1-01D3B50BCA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DA40D0-AC20-4605-9551-D8C7DCFC6621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
   <si>
     <t>アルファ</t>
   </si>
@@ -380,6 +380,10 @@
   </si>
   <si>
     <t>a</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>i</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1639,6 +1643,9 @@
       <c r="I9" t="s">
         <v>66</v>
       </c>
+      <c r="J9" t="s">
+        <v>67</v>
+      </c>
       <c r="L9" s="10"/>
       <c r="M9" s="18">
         <v>8</v>

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirotaRyou\Documents\GitHub\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DA40D0-AC20-4605-9551-D8C7DCFC6621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5271B75B-5DC5-48B2-A3B5-0E12A7511E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="66">
   <si>
     <t>アルファ</t>
   </si>
@@ -372,18 +372,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1コスト：3時間</t>
-    <rPh sb="6" eb="8">
+    <t>1コスト：1.5時間</t>
+    <rPh sb="8" eb="10">
       <t>ジカン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>a</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>i</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1640,12 +1632,6 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="5"/>
-      <c r="I9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" t="s">
-        <v>67</v>
-      </c>
       <c r="L9" s="10"/>
       <c r="M9" s="18">
         <v>8</v>
@@ -1845,7 +1831,9 @@
       <c r="E15" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="4"/>
+      <c r="F15" s="4">
+        <v>2</v>
+      </c>
       <c r="G15" s="4"/>
       <c r="H15" s="5"/>
       <c r="L15" s="10"/>

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirotaRyou\Documents\GitHub\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5271B75B-5DC5-48B2-A3B5-0E12A7511E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB18B6F-2293-4EC7-9A14-F013B8140257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="23550" windowHeight="11295" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="67">
   <si>
     <t>アルファ</t>
   </si>
@@ -376,6 +376,10 @@
     <rPh sb="8" eb="10">
       <t>ジカン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1442,7 +1446,9 @@
       <c r="E4" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="4">
+        <v>3</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="I4" t="s">
         <v>23</v>
@@ -1473,7 +1479,9 @@
       <c r="E5" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="4">
+        <v>2</v>
+      </c>
       <c r="G5" s="4"/>
       <c r="I5" t="s">
         <v>24</v>
@@ -1512,7 +1520,9 @@
       <c r="E6" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="4">
+        <v>2</v>
+      </c>
       <c r="G6" s="4"/>
       <c r="I6" t="s">
         <v>25</v>
@@ -1555,7 +1565,9 @@
       <c r="E7" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4">
+        <v>3</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="5"/>
       <c r="L7" s="19"/>
@@ -1592,7 +1604,9 @@
       <c r="E8" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="4">
+        <v>4</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="5"/>
       <c r="L8" s="6" t="s">
@@ -1629,7 +1643,9 @@
       <c r="E9" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="4">
+        <v>2</v>
+      </c>
       <c r="G9" s="4"/>
       <c r="H9" s="5"/>
       <c r="L9" s="10"/>
@@ -1664,7 +1680,9 @@
       <c r="E10" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="4">
+        <v>2</v>
+      </c>
       <c r="G10" s="4"/>
       <c r="H10" s="5"/>
       <c r="L10" s="10"/>
@@ -1699,7 +1717,9 @@
       <c r="E11" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="4">
+        <v>2</v>
+      </c>
       <c r="G11" s="4"/>
       <c r="H11" s="5"/>
       <c r="L11" s="10"/>
@@ -1734,7 +1754,9 @@
       <c r="E12" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="4"/>
+      <c r="F12" s="4">
+        <v>3</v>
+      </c>
       <c r="G12" s="4"/>
       <c r="H12" s="5"/>
       <c r="L12" s="25"/>
@@ -1759,7 +1781,9 @@
       <c r="E13" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="4"/>
+      <c r="F13" s="4">
+        <v>2</v>
+      </c>
       <c r="G13" s="4"/>
       <c r="H13" t="s">
         <v>16</v>
@@ -1832,7 +1856,7 @@
         <v>48</v>
       </c>
       <c r="F15" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="5"/>
@@ -1868,7 +1892,9 @@
       <c r="E16" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="4"/>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
       <c r="G16" s="4"/>
       <c r="H16" s="5"/>
       <c r="L16" s="10"/>
@@ -1903,7 +1929,9 @@
       <c r="E17" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="4">
+        <v>3</v>
+      </c>
       <c r="G17" s="4"/>
       <c r="H17" s="5"/>
       <c r="L17" s="25"/>
@@ -1932,9 +1960,11 @@
         <v>53</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="F18" s="4">
+        <v>2</v>
+      </c>
       <c r="G18" s="4"/>
       <c r="H18" s="5"/>
     </row>
@@ -1945,9 +1975,11 @@
         <v>54</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="F19" s="4">
+        <v>2</v>
+      </c>
       <c r="G19" s="4"/>
       <c r="H19" s="5"/>
       <c r="L19" s="30"/>
@@ -1964,7 +1996,9 @@
       <c r="E20" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="4"/>
+      <c r="F20" s="4">
+        <v>2</v>
+      </c>
       <c r="G20" s="4"/>
       <c r="H20" s="5"/>
       <c r="L20" s="31"/>
@@ -1981,7 +2015,9 @@
       <c r="E21" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="4"/>
+      <c r="F21" s="4">
+        <v>3</v>
+      </c>
       <c r="G21" s="4"/>
       <c r="H21" s="5"/>
       <c r="L21" s="32"/>
@@ -1998,7 +2034,9 @@
       <c r="E22" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="4"/>
+      <c r="F22" s="4">
+        <v>3</v>
+      </c>
       <c r="G22" s="4"/>
       <c r="H22" s="5"/>
       <c r="L22" s="33"/>
@@ -2015,7 +2053,9 @@
       <c r="E23" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="4"/>
+      <c r="F23" s="4">
+        <v>4</v>
+      </c>
       <c r="G23" s="4"/>
       <c r="H23" s="5"/>
       <c r="L23" s="34"/>
@@ -2031,7 +2071,9 @@
       <c r="E24" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="4"/>
+      <c r="F24" s="4">
+        <v>4</v>
+      </c>
       <c r="G24" s="4"/>
       <c r="H24" s="5"/>
     </row>
@@ -2046,7 +2088,9 @@
       <c r="E25" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="4"/>
+      <c r="F25" s="4">
+        <v>3</v>
+      </c>
       <c r="G25" s="4"/>
       <c r="H25" s="5"/>
     </row>
@@ -2059,7 +2103,9 @@
       <c r="E26" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="4"/>
+      <c r="F26" s="4">
+        <v>3</v>
+      </c>
       <c r="G26" s="4"/>
       <c r="H26" s="5"/>
     </row>
@@ -2072,7 +2118,9 @@
       <c r="E27" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="4"/>
+      <c r="F27" s="4">
+        <v>2</v>
+      </c>
       <c r="G27" s="4"/>
       <c r="H27" s="5"/>
     </row>
@@ -2085,7 +2133,9 @@
       <c r="E28" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="4"/>
+      <c r="F28" s="4">
+        <v>2</v>
+      </c>
       <c r="G28" s="4"/>
       <c r="H28" s="5"/>
     </row>
@@ -2098,7 +2148,9 @@
       <c r="E29" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="4">
+        <v>2</v>
+      </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5"/>
     </row>
@@ -2111,7 +2163,9 @@
       <c r="E30" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F30" s="4"/>
+      <c r="F30" s="4">
+        <v>2</v>
+      </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5"/>
     </row>

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirotaRyou\Documents\GitHub\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB18B6F-2293-4EC7-9A14-F013B8140257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C485644-CBFB-40D4-8E4F-358E68A702AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="23550" windowHeight="11295" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
+    <workbookView xWindow="4410" yWindow="2145" windowWidth="23550" windowHeight="11295" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J6">
         <f>SUM(F38:F51)</f>
-        <v>22.5</v>
+        <v>46.5</v>
       </c>
       <c r="L6" s="10"/>
       <c r="M6" s="18">
@@ -2268,7 +2268,7 @@
         <v>59</v>
       </c>
       <c r="F38" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="5"/>
@@ -2285,7 +2285,7 @@
         <v>48</v>
       </c>
       <c r="F39" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="5"/>
@@ -2300,7 +2300,7 @@
         <v>48</v>
       </c>
       <c r="F40" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="5"/>
@@ -2315,7 +2315,7 @@
         <v>60</v>
       </c>
       <c r="F41" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="5"/>
@@ -2330,7 +2330,7 @@
         <v>60</v>
       </c>
       <c r="F42" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="5"/>
@@ -2345,7 +2345,7 @@
         <v>48</v>
       </c>
       <c r="F43" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="5"/>
@@ -2360,7 +2360,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="5"/>
@@ -2377,7 +2377,7 @@
         <v>48</v>
       </c>
       <c r="F45" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="5"/>
@@ -2392,7 +2392,7 @@
         <v>48</v>
       </c>
       <c r="F46" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="5"/>
@@ -2407,7 +2407,7 @@
         <v>60</v>
       </c>
       <c r="F47" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="5"/>
@@ -2422,7 +2422,7 @@
         <v>60</v>
       </c>
       <c r="F48" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="5"/>
@@ -2437,7 +2437,7 @@
         <v>48</v>
       </c>
       <c r="F49" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="5"/>
@@ -2452,7 +2452,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="5"/>
@@ -2467,7 +2467,7 @@
         <v>63</v>
       </c>
       <c r="F51" s="4">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="5"/>

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirotaRyou\Documents\GitHub\team_khhh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C485644-CBFB-40D4-8E4F-358E68A702AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D79501-8347-42D0-9E48-8F437DC5F6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4410" yWindow="2145" windowWidth="23550" windowHeight="11295" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="67">
   <si>
     <t>アルファ</t>
   </si>
@@ -1346,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71AA7C94-7969-4691-8131-A0EF19A415BF}">
-  <dimension ref="A1:S99"/>
+  <dimension ref="A1:S105"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1528,7 +1528,7 @@
         <v>25</v>
       </c>
       <c r="J6">
-        <f>SUM(F38:F51)</f>
+        <f>SUM(F44:F57)</f>
         <v>46.5</v>
       </c>
       <c r="L6" s="10"/>
@@ -2235,37 +2235,43 @@
     <row r="36" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B36" s="4"/>
       <c r="C36" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="E36" s="36" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F36" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B37" s="41"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="4">
+        <v>3</v>
+      </c>
+      <c r="G37" s="4"/>
       <c r="H37" s="5"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B38" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="E38" s="36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F38" s="4">
         <v>2</v>
@@ -2275,17 +2281,15 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B39" s="4"/>
-      <c r="C39" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F39" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="5"/>
@@ -2294,13 +2298,13 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E40" s="36" t="s">
         <v>48</v>
       </c>
       <c r="F40" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="5"/>
@@ -2309,10 +2313,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F41" s="4">
         <v>2</v>
@@ -2322,45 +2326,41 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="C42" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="4"/>
       <c r="E42" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F42" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="5"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F43" s="4">
-        <v>4</v>
-      </c>
-      <c r="G43" s="4"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
       <c r="H43" s="5"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="B44" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="4"/>
       <c r="E44" s="36" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F44" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="5"/>
@@ -2368,7 +2368,7 @@
     <row r="45" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B45" s="4"/>
       <c r="C45" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>50</v>
@@ -2437,7 +2437,7 @@
         <v>48</v>
       </c>
       <c r="F49" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="5"/>
@@ -2460,70 +2460,76 @@
     <row r="51" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B51" s="4"/>
       <c r="C51" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D51" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="E51" s="36" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F51" s="4">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="5"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B52" s="41"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F52" s="4">
+        <v>4</v>
+      </c>
+      <c r="G52" s="4"/>
       <c r="H52" s="5"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B53" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="E53" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="F53" s="4">
+        <v>2</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="5"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B54" s="4"/>
-      <c r="C54" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="E54" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="F54" s="4">
+        <v>2</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="5"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B55" s="4"/>
-      <c r="C55" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="E55" s="36" t="s">
         <v>48</v>
       </c>
       <c r="F55" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="5"/>
@@ -2531,43 +2537,105 @@
     <row r="56" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="4"/>
+      <c r="D56" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E56" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F56" s="4">
+        <v>4</v>
+      </c>
       <c r="G56" s="4"/>
       <c r="H56" s="5"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
+      <c r="C57" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="D57" s="4"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="4"/>
+      <c r="E57" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F57" s="4">
+        <v>6.5</v>
+      </c>
       <c r="G57" s="4"/>
       <c r="H57" s="5"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="E58" s="35"/>
+      <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="41"/>
       <c r="H58" s="5"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="E59" s="35"/>
+      <c r="B59" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G59" s="4"/>
       <c r="H59" s="5"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="E60" s="35"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G60" s="4"/>
       <c r="H60" s="5"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="E61" s="35"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F61" s="4">
+        <v>4</v>
+      </c>
+      <c r="G61" s="4"/>
       <c r="H61" s="5"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="E62" s="35"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
       <c r="H62" s="5"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="E63" s="35"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
       <c r="H63" s="5"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.4">
@@ -2676,21 +2744,27 @@
     </row>
     <row r="90" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E90" s="35"/>
+      <c r="H90" s="5"/>
     </row>
     <row r="91" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E91" s="35"/>
+      <c r="H91" s="5"/>
     </row>
     <row r="92" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E92" s="35"/>
+      <c r="H92" s="5"/>
     </row>
     <row r="93" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E93" s="35"/>
+      <c r="H93" s="5"/>
     </row>
     <row r="94" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E94" s="35"/>
+      <c r="H94" s="5"/>
     </row>
     <row r="95" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E95" s="35"/>
+      <c r="H95" s="5"/>
     </row>
     <row r="96" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E96" s="35"/>
@@ -2703,6 +2777,24 @@
     </row>
     <row r="99" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E99" s="35"/>
+    </row>
+    <row r="100" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E100" s="35"/>
+    </row>
+    <row r="101" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E101" s="35"/>
+    </row>
+    <row r="102" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E102" s="35"/>
+    </row>
+    <row r="103" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E103" s="35"/>
+    </row>
+    <row r="104" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E104" s="35"/>
+    </row>
+    <row r="105" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E105" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D79501-8347-42D0-9E48-8F437DC5F6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A3C45E-A4EC-4AD0-B737-4CBD4810CD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="67">
   <si>
     <t>アルファ</t>
   </si>
@@ -1528,7 +1528,7 @@
         <v>25</v>
       </c>
       <c r="J6">
-        <f>SUM(F44:F57)</f>
+        <f>SUM(F38:F51)</f>
         <v>46.5</v>
       </c>
       <c r="L6" s="10"/>
@@ -1596,7 +1596,7 @@
     <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B8" s="4"/>
       <c r="C8" s="4" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>50</v>
@@ -1605,7 +1605,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="5"/>
@@ -1644,7 +1644,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="5"/>
@@ -1755,7 +1755,7 @@
         <v>48</v>
       </c>
       <c r="F12" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="5"/>
@@ -2078,200 +2078,194 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="B25" s="4"/>
-      <c r="C25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="4">
-        <v>3</v>
-      </c>
-      <c r="G25" s="4"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4" t="s">
-        <v>51</v>
-      </c>
+      <c r="B26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="4">
-        <v>3</v>
-      </c>
+      <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="C27" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="4"/>
       <c r="E27" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="F27" s="4">
-        <v>2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="C28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="4"/>
       <c r="E28" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="4">
-        <v>2</v>
-      </c>
+      <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4" t="s">
-        <v>47</v>
-      </c>
+      <c r="C29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="4"/>
       <c r="E29" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="4">
-        <v>2</v>
-      </c>
+      <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
+      <c r="C30" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="D30" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E30" s="36" t="s">
         <v>48</v>
       </c>
       <c r="F30" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="4">
+        <v>2</v>
+      </c>
+      <c r="G31" s="4"/>
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="B32" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="E32" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="F32" s="4">
+        <v>2</v>
+      </c>
       <c r="G32" s="4"/>
       <c r="H32" s="5"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B33" s="4"/>
-      <c r="C33" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="E33" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="F33" s="4">
+        <v>2</v>
+      </c>
       <c r="G33" s="4"/>
       <c r="H33" s="5"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B34" s="4"/>
-      <c r="C34" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="E34" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="F34" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="F34" s="4">
+        <v>3</v>
+      </c>
       <c r="G34" s="4"/>
       <c r="H34" s="5"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B35" s="4"/>
-      <c r="C35" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="E35" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="4"/>
+      <c r="F35" s="4">
+        <v>2</v>
+      </c>
       <c r="G35" s="4"/>
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B36" s="4"/>
       <c r="C36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>50</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D36" s="4"/>
       <c r="E36" s="36" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F36" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F37" s="4">
-        <v>3</v>
-      </c>
-      <c r="G37" s="4"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
       <c r="H37" s="5"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="B38" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="4"/>
       <c r="E38" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F38" s="4">
         <v>2</v>
@@ -2281,15 +2275,17 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="D39" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F39" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="5"/>
@@ -2298,13 +2294,13 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E40" s="36" t="s">
         <v>48</v>
       </c>
       <c r="F40" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="5"/>
@@ -2313,10 +2309,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F41" s="4">
         <v>2</v>
@@ -2326,41 +2322,45 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B42" s="4"/>
-      <c r="C42" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="E42" s="36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F42" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="5"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B43" s="41"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" s="4">
+        <v>4</v>
+      </c>
+      <c r="G43" s="4"/>
       <c r="H43" s="5"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B44" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="E44" s="36" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F44" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="5"/>
@@ -2368,7 +2368,7 @@
     <row r="45" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B45" s="4"/>
       <c r="C45" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>50</v>
@@ -2437,7 +2437,7 @@
         <v>48</v>
       </c>
       <c r="F49" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="5"/>
@@ -2460,76 +2460,70 @@
     <row r="51" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B51" s="4"/>
       <c r="C51" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>50</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D51" s="4"/>
       <c r="E51" s="36" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F51" s="4">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="5"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E52" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F52" s="4">
-        <v>4</v>
-      </c>
-      <c r="G52" s="4"/>
+      <c r="B52" s="41"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
       <c r="H52" s="5"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="B53" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="4"/>
       <c r="E53" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="F53" s="4">
-        <v>2</v>
+        <v>61</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="5"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="C54" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" s="4"/>
       <c r="E54" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="F54" s="4">
-        <v>2</v>
+        <v>62</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="5"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4" t="s">
-        <v>47</v>
-      </c>
+      <c r="C55" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="4"/>
       <c r="E55" s="36" t="s">
         <v>48</v>
       </c>
       <c r="F55" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="5"/>
@@ -2537,105 +2531,37 @@
     <row r="56" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
-      <c r="D56" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E56" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F56" s="4">
-        <v>4</v>
-      </c>
+      <c r="D56" s="4"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="5"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B57" s="4"/>
-      <c r="C57" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="C57" s="4"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="F57" s="4">
-        <v>6.5</v>
-      </c>
+      <c r="E57" s="36"/>
+      <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="5"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B58" s="41"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
       <c r="H58" s="5"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B59" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G59" s="4"/>
       <c r="H59" s="5"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B60" s="4"/>
-      <c r="C60" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G60" s="4"/>
       <c r="H60" s="5"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B61" s="4"/>
-      <c r="C61" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F61" s="4">
-        <v>4</v>
-      </c>
-      <c r="G61" s="4"/>
       <c r="H61" s="5"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="36"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
       <c r="H62" s="5"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="36"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
       <c r="H63" s="5"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.4">

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A3C45E-A4EC-4AD0-B737-4CBD4810CD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66C62E6-300E-48D7-ABFC-9AF48F755B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="71">
   <si>
     <t>アルファ</t>
   </si>
@@ -298,34 +298,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1攻撃</t>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2攻撃</t>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3攻撃</t>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>4攻撃</t>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スタミナ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -379,7 +351,69 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>B</t>
+    <t>ランダム移動</t>
+    <rPh sb="4" eb="6">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>突進攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>トッシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近接攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>キンセツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠距離攻撃</t>
+    <rPh sb="0" eb="3">
+      <t>エンキョリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2段ジャンプ</t>
+    <rPh sb="1" eb="2">
+      <t>ダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近接攻撃</t>
+    <rPh sb="0" eb="4">
+      <t>キンセツコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つかみ攻撃</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1346,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71AA7C94-7969-4691-8131-A0EF19A415BF}">
-  <dimension ref="A1:S105"/>
+  <dimension ref="A1:S102"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1358,7 +1392,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.4">
@@ -1415,7 +1449,7 @@
         <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" t="s">
@@ -1480,7 +1514,7 @@
         <v>48</v>
       </c>
       <c r="F5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4"/>
       <c r="I5" t="s">
@@ -1521,15 +1555,15 @@
         <v>48</v>
       </c>
       <c r="F6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4"/>
       <c r="I6" t="s">
         <v>25</v>
       </c>
       <c r="J6">
-        <f>SUM(F38:F51)</f>
-        <v>46.5</v>
+        <f>SUM(F37:F53)</f>
+        <v>48.5</v>
       </c>
       <c r="L6" s="10"/>
       <c r="M6" s="18">
@@ -1566,7 +1600,7 @@
         <v>48</v>
       </c>
       <c r="F7" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="5"/>
@@ -1599,7 +1633,7 @@
         <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>48</v>
@@ -1638,7 +1672,7 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E9" s="36" t="s">
         <v>48</v>
@@ -1675,13 +1709,13 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F10" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="5"/>
@@ -1712,13 +1746,13 @@
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="5"/>
@@ -1755,7 +1789,7 @@
         <v>48</v>
       </c>
       <c r="F12" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="5"/>
@@ -1782,7 +1816,7 @@
         <v>48</v>
       </c>
       <c r="F13" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" t="s">
@@ -1887,7 +1921,7 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E16" s="36" t="s">
         <v>48</v>
@@ -1924,10 +1958,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F17" s="4">
         <v>3</v>
@@ -1957,10 +1991,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F18" s="4">
         <v>2</v>
@@ -1972,10 +2006,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F19" s="4">
         <v>2</v>
@@ -2029,7 +2063,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E22" s="36" t="s">
         <v>48</v>
@@ -2048,7 +2082,7 @@
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E23" s="36" t="s">
         <v>48</v>
@@ -2066,7 +2100,7 @@
     <row r="24" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E24" s="36" t="s">
         <v>48</v>
@@ -2121,7 +2155,7 @@
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -2146,7 +2180,7 @@
         <v>39</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E30" s="36" t="s">
         <v>48</v>
@@ -2161,7 +2195,7 @@
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E31" s="36" t="s">
         <v>48</v>
@@ -2176,10 +2210,10 @@
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F32" s="4">
         <v>2</v>
@@ -2191,13 +2225,13 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F33" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="5"/>
@@ -2206,80 +2240,80 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E34" s="36" t="s">
         <v>48</v>
       </c>
       <c r="F34" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="5"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="C35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="4"/>
       <c r="E35" s="36" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F35" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="F36" s="4">
-        <v>1</v>
-      </c>
-      <c r="G36" s="4"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B37" s="41"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
+      <c r="B37" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="4">
+        <v>2</v>
+      </c>
+      <c r="G37" s="4"/>
       <c r="H37" s="5"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B38" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="B38" s="4"/>
       <c r="C38" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="E38" s="36" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F38" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="5"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B39" s="4"/>
-      <c r="C39" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E39" s="36" t="s">
         <v>48</v>
@@ -2294,7 +2328,7 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E40" s="36" t="s">
         <v>48</v>
@@ -2309,28 +2343,30 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F41" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="5"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
+      <c r="C42" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="D42" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F42" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="5"/>
@@ -2339,7 +2375,7 @@
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="E43" s="36" t="s">
         <v>48</v>
@@ -2354,30 +2390,28 @@
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E44" s="36" t="s">
         <v>48</v>
       </c>
       <c r="F44" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="5"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B45" s="4"/>
-      <c r="C45" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="C45" s="4"/>
       <c r="D45" s="4" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E45" s="36" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F45" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="5"/>
@@ -2386,13 +2420,13 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E46" s="36" t="s">
         <v>48</v>
       </c>
       <c r="F46" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="5"/>
@@ -2401,10 +2435,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E47" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F47" s="4">
         <v>2</v>
@@ -2416,43 +2450,39 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F48" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="5"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F49" s="4">
-        <v>2</v>
-      </c>
-      <c r="G49" s="4"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
       <c r="H49" s="5"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="B50" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" s="4"/>
       <c r="E50" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F50" s="4">
-        <v>4</v>
+        <v>57</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="5"/>
@@ -2460,90 +2490,64 @@
     <row r="51" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B51" s="4"/>
       <c r="C51" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="F51" s="4">
-        <v>6.5</v>
+        <v>58</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="5"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B52" s="41"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F52" s="4">
+        <v>4</v>
+      </c>
+      <c r="G52" s="4"/>
       <c r="H52" s="5"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B53" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="B53" s="4"/>
       <c r="C53" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="F53" s="4">
+        <v>6.5</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="5"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B54" s="4"/>
-      <c r="C54" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="C54" s="4"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="E54" s="36"/>
+      <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="5"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B55" s="4"/>
-      <c r="C55" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F55" s="4">
-        <v>4</v>
-      </c>
-      <c r="G55" s="4"/>
       <c r="H55" s="5"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
       <c r="H56" s="5"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
       <c r="H57" s="5"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.4">
@@ -2556,12 +2560,15 @@
       <c r="H60" s="5"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="E61" s="35"/>
       <c r="H61" s="5"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="E62" s="35"/>
       <c r="H62" s="5"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="E63" s="35"/>
       <c r="H63" s="5"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.4">
@@ -2682,15 +2689,12 @@
     </row>
     <row r="93" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E93" s="35"/>
-      <c r="H93" s="5"/>
     </row>
     <row r="94" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E94" s="35"/>
-      <c r="H94" s="5"/>
     </row>
     <row r="95" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E95" s="35"/>
-      <c r="H95" s="5"/>
     </row>
     <row r="96" spans="5:8" x14ac:dyDescent="0.4">
       <c r="E96" s="35"/>
@@ -2712,15 +2716,6 @@
     </row>
     <row r="102" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E102" s="35"/>
-    </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E103" s="35"/>
-    </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E104" s="35"/>
-    </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E105" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirakiRyou\Desktop\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A3C45E-A4EC-4AD0-B737-4CBD4810CD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055BAFC7-149D-47B9-98E1-F1EA47F2E5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="61">
   <si>
     <t>アルファ</t>
   </si>
@@ -187,13 +187,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>シーン全般</t>
-    <rPh sb="3" eb="5">
-      <t>ゼンパン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>デバック</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -201,16 +194,6 @@
     <t>全員</t>
     <rPh sb="0" eb="2">
       <t>ゼンイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>手伝い（終わってないバカのため）</t>
-    <rPh sb="0" eb="2">
-      <t>テツダ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -287,10 +270,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>動き</t>
     <rPh sb="0" eb="1">
       <t>ウゴ</t>
@@ -348,27 +327,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>SSSSS</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>E</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>GOD</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>B&gt;=x&lt;=S</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>∞</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -380,6 +343,13 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手伝い</t>
+    <rPh sb="0" eb="2">
+      <t>テツダ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1358,7 +1328,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.4">
@@ -1369,10 +1339,10 @@
         <v>15</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>1</v>
@@ -1408,15 +1378,11 @@
         <v>21</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3" s="4"/>
-      <c r="E3" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="E3" s="36"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" t="s">
         <v>3</v>
@@ -1438,13 +1404,13 @@
     <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F4" s="4">
         <v>3</v>
@@ -1471,13 +1437,13 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
@@ -1512,13 +1478,13 @@
     <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B6" s="4"/>
       <c r="C6" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F6" s="4">
         <v>2</v>
@@ -1529,7 +1495,7 @@
       </c>
       <c r="J6">
         <f>SUM(F38:F51)</f>
-        <v>46.5</v>
+        <v>40</v>
       </c>
       <c r="L6" s="10"/>
       <c r="M6" s="18">
@@ -1557,13 +1523,13 @@
     <row r="7" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F7" s="4">
         <v>3</v>
@@ -1599,10 +1565,10 @@
         <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -1638,10 +1604,10 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F9" s="4">
         <v>3</v>
@@ -1675,10 +1641,10 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F10" s="4">
         <v>2</v>
@@ -1712,10 +1678,10 @@
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F11" s="4">
         <v>2</v>
@@ -1749,10 +1715,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -1776,10 +1742,10 @@
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F13" s="4">
         <v>2</v>
@@ -1847,13 +1813,13 @@
         <v>23</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="E15" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F15" s="4">
         <v>4</v>
@@ -1887,10 +1853,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F16" s="4">
         <v>3</v>
@@ -1924,10 +1890,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F17" s="4">
         <v>3</v>
@@ -1957,10 +1923,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4">
         <v>2</v>
@@ -1972,10 +1938,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F19" s="4">
         <v>2</v>
@@ -1991,10 +1957,10 @@
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F20" s="4">
         <v>2</v>
@@ -2010,10 +1976,10 @@
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F21" s="4">
         <v>3</v>
@@ -2029,10 +1995,10 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F22" s="4">
         <v>3</v>
@@ -2048,10 +2014,10 @@
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F23" s="4">
         <v>4</v>
@@ -2066,10 +2032,10 @@
     <row r="24" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F24" s="4">
         <v>4</v>
@@ -2095,7 +2061,7 @@
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -2108,7 +2074,7 @@
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -2121,7 +2087,7 @@
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -2130,11 +2096,11 @@
     <row r="29" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -2143,13 +2109,13 @@
     <row r="30" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B30" s="4"/>
       <c r="C30" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F30" s="4">
         <v>4</v>
@@ -2161,10 +2127,10 @@
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F31" s="4">
         <v>2</v>
@@ -2176,10 +2142,10 @@
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F32" s="4">
         <v>2</v>
@@ -2191,10 +2157,10 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F33" s="4">
         <v>2</v>
@@ -2206,10 +2172,10 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F34" s="4">
         <v>3</v>
@@ -2221,10 +2187,10 @@
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F35" s="4">
         <v>2</v>
@@ -2235,11 +2201,11 @@
     <row r="36" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B36" s="4"/>
       <c r="C36" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="36" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F36" s="4">
         <v>1</v>
@@ -2261,11 +2227,11 @@
         <v>25</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="36" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F38" s="4">
         <v>2</v>
@@ -2279,10 +2245,10 @@
         <v>30</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F39" s="4">
         <v>4</v>
@@ -2294,10 +2260,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F40" s="4">
         <v>4</v>
@@ -2309,10 +2275,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F41" s="4">
         <v>2</v>
@@ -2324,10 +2290,10 @@
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F42" s="4">
         <v>2</v>
@@ -2339,10 +2305,10 @@
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E43" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F43" s="4">
         <v>4</v>
@@ -2354,10 +2320,10 @@
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E44" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F44" s="4">
         <v>4</v>
@@ -2371,10 +2337,10 @@
         <v>31</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E45" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F45" s="4">
         <v>4</v>
@@ -2386,10 +2352,10 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E46" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F46" s="4">
         <v>4</v>
@@ -2401,10 +2367,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E47" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F47" s="4">
         <v>2</v>
@@ -2416,10 +2382,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F48" s="4">
         <v>2</v>
@@ -2431,10 +2397,10 @@
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E49" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F49" s="4">
         <v>2</v>
@@ -2446,10 +2412,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E50" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F50" s="4">
         <v>4</v>
@@ -2459,16 +2425,10 @@
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B51" s="4"/>
-      <c r="C51" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="C51" s="4"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="F51" s="4">
-        <v>6.5</v>
-      </c>
+      <c r="E51" s="36"/>
+      <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="5"/>
     </row>
@@ -2483,33 +2443,29 @@
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B53" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="5"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B54" s="4"/>
       <c r="C54" s="4" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="5"/>
     </row>
@@ -2520,7 +2476,7 @@
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F55" s="4">
         <v>4</v>

--- a/チーム製作コスト表.xlsx
+++ b/チーム製作コスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirakiRyou\Desktop\GitHub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055BAFC7-149D-47B9-98E1-F1EA47F2E5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EAE859-C385-4C0F-A83E-F7A1E4D63D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE05E658-BBB7-43F4-857C-7948D261B06D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="63">
   <si>
     <t>アルファ</t>
   </si>
@@ -298,21 +298,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4攻撃</t>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スタミナ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>回避</t>
-    <rPh sb="0" eb="2">
-      <t>カイヒ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -342,14 +328,45 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>B</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>手伝い</t>
     <rPh sb="0" eb="2">
       <t>テツダ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近接攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>キンセツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠距離攻撃</t>
+    <rPh sb="0" eb="3">
+      <t>エンキョリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2段ジャンプ</t>
+    <rPh sb="1" eb="2">
+      <t>ダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1328,7 +1345,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.4">
@@ -1644,7 +1661,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F10" s="4">
         <v>2</v>
@@ -1681,7 +1698,7 @@
         <v>50</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F11" s="4">
         <v>2</v>
@@ -1853,7 +1870,7 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E16" s="36" t="s">
         <v>46</v>
@@ -1890,10 +1907,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F17" s="4">
         <v>3</v>
@@ -1923,10 +1940,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F18" s="4">
         <v>2</v>
@@ -1938,10 +1955,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F19" s="4">
         <v>2</v>
@@ -1995,7 +2012,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E22" s="36" t="s">
         <v>46</v>
@@ -2014,7 +2031,7 @@
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E23" s="36" t="s">
         <v>46</v>
@@ -2032,7 +2049,7 @@
     <row r="24" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E24" s="36" t="s">
         <v>46</v>
@@ -2087,7 +2104,7 @@
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -2145,7 +2162,7 @@
         <v>49</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F32" s="4">
         <v>2</v>
@@ -2160,7 +2177,7 @@
         <v>50</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F33" s="4">
         <v>2</v>
@@ -2201,7 +2218,7 @@
     <row r="36" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B36" s="4"/>
       <c r="C36" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="36" t="s">
@@ -2227,7 +2244,7 @@
         <v>25</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="36" t="s">
@@ -2278,7 +2295,7 @@
         <v>49</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F41" s="4">
         <v>2</v>
@@ -2293,7 +2310,7 @@
         <v>50</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F42" s="4">
         <v>2</v>
@@ -2370,7 +2387,7 @@
         <v>49</v>
       </c>
       <c r="E47" s="36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F47" s="4">
         <v>2</v>
@@ -2385,7 +2402,7 @@
         <v>50</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F48" s="4">
         <v>2</v>
@@ -2450,7 +2467,7 @@
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
@@ -2459,7 +2476,7 @@
     <row r="54" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B54" s="4"/>
       <c r="C54" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="36" t="s">
